--- a/reference/Municípios RS visitados.xlsx
+++ b/reference/Municípios RS visitados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SAPDevelop\Repos\projeto-497\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6D1EB4-43A3-49FB-A18A-7200BA5B7E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699764F9-E953-4A3B-8786-C909C5810091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2887" uniqueCount="764">
   <si>
     <t>Estado</t>
   </si>
@@ -2334,6 +2334,9 @@
   </si>
   <si>
     <t>São Bonifácio</t>
+  </si>
+  <si>
+    <t>São Brás</t>
   </si>
 </sst>
 </file>
@@ -2677,7 +2680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2818,6 +2821,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3052,7 +3056,7 @@
     <col min="12" max="12" width="16.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:30" ht="14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3090,7 +3094,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:30" ht="14">
       <c r="A2" s="6" t="e">
         <f t="shared" ref="A2:A146" ca="1" si="0">_xludf.CONCAT(C2," (RS)")</f>
         <v>#NAME?</v>
@@ -3132,7 +3136,7 @@
       </c>
       <c r="O2" s="13"/>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:30" ht="14">
       <c r="A3" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3176,11 +3180,11 @@
       </c>
       <c r="N3" s="22">
         <f>497-COUNTIF(J2:J503,"")</f>
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O3" s="23">
         <f>N3/$N$2</f>
-        <v>0.63581488933601604</v>
+        <v>0.6378269617706237</v>
       </c>
       <c r="P3" s="24"/>
       <c r="Q3" s="24"/>
@@ -3198,7 +3202,7 @@
       <c r="AC3" s="24"/>
       <c r="AD3" s="24"/>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:30" ht="14">
       <c r="A4" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3242,11 +3246,11 @@
       </c>
       <c r="N4" s="13">
         <f>497-N3</f>
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O4" s="33"/>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:30" ht="14">
       <c r="A5" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3291,7 +3295,7 @@
         <v>0.14084507042253522</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:30" ht="14">
       <c r="A6" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3325,7 +3329,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:30" ht="14">
       <c r="A7" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3360,7 +3364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:30" ht="14">
       <c r="A8" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3394,7 +3398,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:30" ht="14">
       <c r="A9" s="36" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3452,7 +3456,7 @@
       <c r="AC9" s="43"/>
       <c r="AD9" s="43"/>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:30" ht="14">
       <c r="A10" s="36" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3510,7 +3514,7 @@
       <c r="AC10" s="43"/>
       <c r="AD10" s="43"/>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:30" ht="14">
       <c r="A11" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3544,7 +3548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:30" ht="14">
       <c r="A12" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3602,7 +3606,7 @@
       <c r="AC12" s="24"/>
       <c r="AD12" s="24"/>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:30" ht="14">
       <c r="A13" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3660,7 +3664,7 @@
       <c r="AC13" s="21"/>
       <c r="AD13" s="21"/>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:30" ht="14">
       <c r="A14" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3694,7 +3698,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:30" ht="14">
       <c r="A15" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3734,7 +3738,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:30" ht="14">
       <c r="A16" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3792,7 +3796,7 @@
       <c r="AC16" s="32"/>
       <c r="AD16" s="32"/>
     </row>
-    <row r="17" spans="1:30">
+    <row r="17" spans="1:30" ht="14">
       <c r="A17" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3850,7 +3854,7 @@
       <c r="AC17" s="21"/>
       <c r="AD17" s="21"/>
     </row>
-    <row r="18" spans="1:30">
+    <row r="18" spans="1:30" ht="14">
       <c r="A18" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3908,7 +3912,7 @@
       <c r="AC18" s="24"/>
       <c r="AD18" s="24"/>
     </row>
-    <row r="19" spans="1:30">
+    <row r="19" spans="1:30" ht="14">
       <c r="A19" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -3966,7 +3970,7 @@
       <c r="AC19" s="21"/>
       <c r="AD19" s="21"/>
     </row>
-    <row r="20" spans="1:30">
+    <row r="20" spans="1:30" ht="14">
       <c r="A20" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4024,7 +4028,7 @@
       <c r="AC20" s="24"/>
       <c r="AD20" s="24"/>
     </row>
-    <row r="21" spans="1:30">
+    <row r="21" spans="1:30" ht="14">
       <c r="A21" s="36" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4082,7 +4086,7 @@
       <c r="AC21" s="43"/>
       <c r="AD21" s="43"/>
     </row>
-    <row r="22" spans="1:30">
+    <row r="22" spans="1:30" ht="14">
       <c r="A22" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4140,7 +4144,7 @@
       <c r="AC22" s="32"/>
       <c r="AD22" s="32"/>
     </row>
-    <row r="23" spans="1:30">
+    <row r="23" spans="1:30" ht="14">
       <c r="A23" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4174,7 +4178,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:30">
+    <row r="24" spans="1:30" ht="14">
       <c r="A24" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4232,7 +4236,7 @@
       <c r="AC24" s="21"/>
       <c r="AD24" s="21"/>
     </row>
-    <row r="25" spans="1:30">
+    <row r="25" spans="1:30" ht="14">
       <c r="A25" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4266,7 +4270,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:30">
+    <row r="26" spans="1:30" ht="14">
       <c r="A26" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4300,7 +4304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:30">
+    <row r="27" spans="1:30" ht="14">
       <c r="A27" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4358,7 +4362,7 @@
       <c r="AC27" s="24"/>
       <c r="AD27" s="24"/>
     </row>
-    <row r="28" spans="1:30">
+    <row r="28" spans="1:30" ht="14">
       <c r="A28" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4416,7 +4420,7 @@
       <c r="AC28" s="24"/>
       <c r="AD28" s="24"/>
     </row>
-    <row r="29" spans="1:30">
+    <row r="29" spans="1:30" ht="14">
       <c r="A29" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4450,7 +4454,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:30">
+    <row r="30" spans="1:30" ht="14">
       <c r="A30" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4508,7 +4512,7 @@
       <c r="AC30" s="32"/>
       <c r="AD30" s="32"/>
     </row>
-    <row r="31" spans="1:30">
+    <row r="31" spans="1:30" ht="14">
       <c r="A31" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4562,7 +4566,7 @@
       <c r="AC31" s="60"/>
       <c r="AD31" s="60"/>
     </row>
-    <row r="32" spans="1:30">
+    <row r="32" spans="1:30" ht="14">
       <c r="A32" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4620,7 +4624,7 @@
       <c r="AC32" s="24"/>
       <c r="AD32" s="24"/>
     </row>
-    <row r="33" spans="1:30">
+    <row r="33" spans="1:30" ht="14">
       <c r="A33" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4678,7 +4682,7 @@
       <c r="AC33" s="21"/>
       <c r="AD33" s="21"/>
     </row>
-    <row r="34" spans="1:30">
+    <row r="34" spans="1:30" ht="14">
       <c r="A34" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4708,11 +4712,17 @@
       <c r="I34" s="12" t="s">
         <v>19</v>
       </c>
+      <c r="J34" s="70">
+        <v>44844</v>
+      </c>
+      <c r="K34" s="114" t="s">
+        <v>763</v>
+      </c>
       <c r="L34" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:30">
+    <row r="35" spans="1:30" ht="14">
       <c r="A35" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4746,7 +4756,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:30">
+    <row r="36" spans="1:30" ht="14">
       <c r="A36" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4780,7 +4790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:30">
+    <row r="37" spans="1:30" ht="14">
       <c r="A37" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4814,7 +4824,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:30">
+    <row r="38" spans="1:30" ht="14">
       <c r="A38" s="61" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4872,7 +4882,7 @@
       <c r="AC38" s="69"/>
       <c r="AD38" s="69"/>
     </row>
-    <row r="39" spans="1:30">
+    <row r="39" spans="1:30" ht="14">
       <c r="A39" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4912,7 +4922,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:30">
+    <row r="40" spans="1:30" ht="14">
       <c r="A40" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -4946,7 +4956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:30">
+    <row r="41" spans="1:30" ht="14">
       <c r="A41" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5004,7 +5014,7 @@
       <c r="AC41" s="24"/>
       <c r="AD41" s="24"/>
     </row>
-    <row r="42" spans="1:30">
+    <row r="42" spans="1:30" ht="14">
       <c r="A42" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5062,7 +5072,7 @@
       <c r="AC42" s="32"/>
       <c r="AD42" s="32"/>
     </row>
-    <row r="43" spans="1:30">
+    <row r="43" spans="1:30" ht="14">
       <c r="A43" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5102,7 +5112,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:30">
+    <row r="44" spans="1:30" ht="14">
       <c r="A44" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5160,7 +5170,7 @@
       <c r="AC44" s="24"/>
       <c r="AD44" s="24"/>
     </row>
-    <row r="45" spans="1:30">
+    <row r="45" spans="1:30" ht="14">
       <c r="A45" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5194,7 +5204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:30">
+    <row r="46" spans="1:30" ht="14">
       <c r="A46" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5228,7 +5238,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:30">
+    <row r="47" spans="1:30" ht="14">
       <c r="A47" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5262,7 +5272,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:30">
+    <row r="48" spans="1:30" ht="14">
       <c r="A48" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5296,7 +5306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:30">
+    <row r="49" spans="1:30" ht="14">
       <c r="A49" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5354,7 +5364,7 @@
       <c r="AC49" s="21"/>
       <c r="AD49" s="21"/>
     </row>
-    <row r="50" spans="1:30">
+    <row r="50" spans="1:30" ht="14">
       <c r="A50" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5412,7 +5422,7 @@
       <c r="AC50" s="24"/>
       <c r="AD50" s="24"/>
     </row>
-    <row r="51" spans="1:30">
+    <row r="51" spans="1:30" ht="14">
       <c r="A51" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5470,7 +5480,7 @@
       <c r="AC51" s="24"/>
       <c r="AD51" s="24"/>
     </row>
-    <row r="52" spans="1:30">
+    <row r="52" spans="1:30" ht="14">
       <c r="A52" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5504,7 +5514,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:30">
+    <row r="53" spans="1:30" ht="14">
       <c r="A53" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5562,7 +5572,7 @@
       <c r="AC53" s="32"/>
       <c r="AD53" s="32"/>
     </row>
-    <row r="54" spans="1:30">
+    <row r="54" spans="1:30" ht="14">
       <c r="A54" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5620,7 +5630,7 @@
       <c r="AC54" s="32"/>
       <c r="AD54" s="32"/>
     </row>
-    <row r="55" spans="1:30">
+    <row r="55" spans="1:30" ht="14">
       <c r="A55" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5654,7 +5664,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:30">
+    <row r="56" spans="1:30" ht="14">
       <c r="A56" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5712,7 +5722,7 @@
       <c r="AC56" s="21"/>
       <c r="AD56" s="21"/>
     </row>
-    <row r="57" spans="1:30">
+    <row r="57" spans="1:30" ht="14">
       <c r="A57" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5746,7 +5756,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:30">
+    <row r="58" spans="1:30" ht="14">
       <c r="A58" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5804,7 +5814,7 @@
       <c r="AC58" s="24"/>
       <c r="AD58" s="24"/>
     </row>
-    <row r="59" spans="1:30">
+    <row r="59" spans="1:30" ht="14">
       <c r="A59" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5838,7 +5848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:30">
+    <row r="60" spans="1:30" ht="14">
       <c r="A60" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5872,7 +5882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:30">
+    <row r="61" spans="1:30" ht="14">
       <c r="A61" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5906,7 +5916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:30">
+    <row r="62" spans="1:30" ht="14">
       <c r="A62" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5940,7 +5950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:30">
+    <row r="63" spans="1:30" ht="14">
       <c r="A63" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -5998,7 +6008,7 @@
       <c r="AC63" s="24"/>
       <c r="AD63" s="24"/>
     </row>
-    <row r="64" spans="1:30">
+    <row r="64" spans="1:30" ht="14">
       <c r="A64" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6056,7 +6066,7 @@
       <c r="AC64" s="24"/>
       <c r="AD64" s="24"/>
     </row>
-    <row r="65" spans="1:30">
+    <row r="65" spans="1:30" ht="14">
       <c r="A65" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6114,7 +6124,7 @@
       <c r="AC65" s="24"/>
       <c r="AD65" s="24"/>
     </row>
-    <row r="66" spans="1:30">
+    <row r="66" spans="1:30" ht="14">
       <c r="A66" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6148,7 +6158,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:30">
+    <row r="67" spans="1:30" ht="14">
       <c r="A67" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6206,7 +6216,7 @@
       <c r="AC67" s="24"/>
       <c r="AD67" s="24"/>
     </row>
-    <row r="68" spans="1:30">
+    <row r="68" spans="1:30" ht="14">
       <c r="A68" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6264,7 +6274,7 @@
       <c r="AC68" s="21"/>
       <c r="AD68" s="21"/>
     </row>
-    <row r="69" spans="1:30">
+    <row r="69" spans="1:30" ht="14">
       <c r="A69" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6322,7 +6332,7 @@
       <c r="AC69" s="24"/>
       <c r="AD69" s="24"/>
     </row>
-    <row r="70" spans="1:30">
+    <row r="70" spans="1:30" ht="14">
       <c r="A70" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6380,7 +6390,7 @@
       <c r="AC70" s="24"/>
       <c r="AD70" s="24"/>
     </row>
-    <row r="71" spans="1:30">
+    <row r="71" spans="1:30" ht="14">
       <c r="A71" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6414,7 +6424,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:30">
+    <row r="72" spans="1:30" ht="14">
       <c r="A72" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6454,7 +6464,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:30">
+    <row r="73" spans="1:30" ht="14">
       <c r="A73" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6512,7 +6522,7 @@
       <c r="AC73" s="24"/>
       <c r="AD73" s="24"/>
     </row>
-    <row r="74" spans="1:30">
+    <row r="74" spans="1:30" ht="14">
       <c r="A74" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6546,7 +6556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:30">
+    <row r="75" spans="1:30" ht="14">
       <c r="A75" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6580,7 +6590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:30">
+    <row r="76" spans="1:30" ht="14">
       <c r="A76" s="79" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6623,7 +6633,7 @@
       <c r="N76" s="32"/>
       <c r="O76" s="32"/>
     </row>
-    <row r="77" spans="1:30">
+    <row r="77" spans="1:30" ht="14">
       <c r="A77" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6672,7 +6682,7 @@
       <c r="AC77" s="32"/>
       <c r="AD77" s="32"/>
     </row>
-    <row r="78" spans="1:30">
+    <row r="78" spans="1:30" ht="14">
       <c r="A78" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6706,7 +6716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:30">
+    <row r="79" spans="1:30" ht="14">
       <c r="A79" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6764,7 +6774,7 @@
       <c r="AC79" s="24"/>
       <c r="AD79" s="24"/>
     </row>
-    <row r="80" spans="1:30">
+    <row r="80" spans="1:30" ht="14">
       <c r="A80" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6798,7 +6808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:30">
+    <row r="81" spans="1:30" ht="14">
       <c r="A81" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6856,7 +6866,7 @@
       <c r="AC81" s="24"/>
       <c r="AD81" s="24"/>
     </row>
-    <row r="82" spans="1:30">
+    <row r="82" spans="1:30" ht="14">
       <c r="A82" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6914,7 +6924,7 @@
       <c r="AC82" s="32"/>
       <c r="AD82" s="32"/>
     </row>
-    <row r="83" spans="1:30">
+    <row r="83" spans="1:30" ht="14">
       <c r="A83" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -6972,7 +6982,7 @@
       <c r="AC83" s="24"/>
       <c r="AD83" s="24"/>
     </row>
-    <row r="84" spans="1:30">
+    <row r="84" spans="1:30" ht="14">
       <c r="A84" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7030,7 +7040,7 @@
       <c r="AC84" s="24"/>
       <c r="AD84" s="24"/>
     </row>
-    <row r="85" spans="1:30">
+    <row r="85" spans="1:30" ht="14">
       <c r="A85" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7064,7 +7074,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:30">
+    <row r="86" spans="1:30" ht="14">
       <c r="A86" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7122,7 +7132,7 @@
       <c r="AC86" s="24"/>
       <c r="AD86" s="24"/>
     </row>
-    <row r="87" spans="1:30">
+    <row r="87" spans="1:30" ht="14">
       <c r="A87" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7180,7 +7190,7 @@
       <c r="AC87" s="24"/>
       <c r="AD87" s="24"/>
     </row>
-    <row r="88" spans="1:30">
+    <row r="88" spans="1:30" ht="14">
       <c r="A88" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7238,7 +7248,7 @@
       <c r="AC88" s="24"/>
       <c r="AD88" s="24"/>
     </row>
-    <row r="89" spans="1:30">
+    <row r="89" spans="1:30" ht="14">
       <c r="A89" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7296,7 +7306,7 @@
       <c r="AC89" s="24"/>
       <c r="AD89" s="24"/>
     </row>
-    <row r="90" spans="1:30">
+    <row r="90" spans="1:30" ht="14">
       <c r="A90" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7354,7 +7364,7 @@
       <c r="AC90" s="24"/>
       <c r="AD90" s="24"/>
     </row>
-    <row r="91" spans="1:30">
+    <row r="91" spans="1:30" ht="14">
       <c r="A91" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7412,7 +7422,7 @@
       <c r="AC91" s="24"/>
       <c r="AD91" s="24"/>
     </row>
-    <row r="92" spans="1:30">
+    <row r="92" spans="1:30" ht="14">
       <c r="A92" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7470,7 +7480,7 @@
       <c r="AC92" s="24"/>
       <c r="AD92" s="24"/>
     </row>
-    <row r="93" spans="1:30">
+    <row r="93" spans="1:30" ht="14">
       <c r="A93" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7528,7 +7538,7 @@
       <c r="AC93" s="32"/>
       <c r="AD93" s="32"/>
     </row>
-    <row r="94" spans="1:30">
+    <row r="94" spans="1:30" ht="14">
       <c r="A94" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7586,7 +7596,7 @@
       <c r="AC94" s="24"/>
       <c r="AD94" s="24"/>
     </row>
-    <row r="95" spans="1:30">
+    <row r="95" spans="1:30" ht="14">
       <c r="A95" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7644,7 +7654,7 @@
       <c r="AC95" s="24"/>
       <c r="AD95" s="24"/>
     </row>
-    <row r="96" spans="1:30">
+    <row r="96" spans="1:30" ht="14">
       <c r="A96" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7678,7 +7688,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:30">
+    <row r="97" spans="1:30" ht="14">
       <c r="A97" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7736,7 +7746,7 @@
       <c r="AC97" s="24"/>
       <c r="AD97" s="24"/>
     </row>
-    <row r="98" spans="1:30">
+    <row r="98" spans="1:30" ht="14">
       <c r="A98" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7794,7 +7804,7 @@
       <c r="AC98" s="32"/>
       <c r="AD98" s="32"/>
     </row>
-    <row r="99" spans="1:30">
+    <row r="99" spans="1:30" ht="14">
       <c r="A99" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7852,7 +7862,7 @@
       <c r="AC99" s="24"/>
       <c r="AD99" s="24"/>
     </row>
-    <row r="100" spans="1:30">
+    <row r="100" spans="1:30" ht="14">
       <c r="A100" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7886,7 +7896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:30">
+    <row r="101" spans="1:30" ht="14">
       <c r="A101" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7920,7 +7930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:30">
+    <row r="102" spans="1:30" ht="14">
       <c r="A102" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7954,7 +7964,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:30">
+    <row r="103" spans="1:30" ht="14">
       <c r="A103" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -7988,7 +7998,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:30">
+    <row r="104" spans="1:30" ht="14">
       <c r="A104" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8022,7 +8032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:30">
+    <row r="105" spans="1:30" ht="14">
       <c r="A105" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8080,7 +8090,7 @@
       <c r="AC105" s="32"/>
       <c r="AD105" s="32"/>
     </row>
-    <row r="106" spans="1:30">
+    <row r="106" spans="1:30" ht="14">
       <c r="A106" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8138,7 +8148,7 @@
       <c r="AC106" s="32"/>
       <c r="AD106" s="32"/>
     </row>
-    <row r="107" spans="1:30">
+    <row r="107" spans="1:30" ht="14">
       <c r="A107" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8172,7 +8182,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:30">
+    <row r="108" spans="1:30" ht="14">
       <c r="A108" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8206,7 +8216,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="109" spans="1:30">
+    <row r="109" spans="1:30" ht="14">
       <c r="A109" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8240,7 +8250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="1:30">
+    <row r="110" spans="1:30" ht="14">
       <c r="A110" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8298,7 +8308,7 @@
       <c r="AC110" s="24"/>
       <c r="AD110" s="24"/>
     </row>
-    <row r="111" spans="1:30">
+    <row r="111" spans="1:30" ht="14">
       <c r="A111" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8356,7 +8366,7 @@
       <c r="AC111" s="24"/>
       <c r="AD111" s="24"/>
     </row>
-    <row r="112" spans="1:30">
+    <row r="112" spans="1:30" ht="14">
       <c r="A112" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8414,7 +8424,7 @@
       <c r="AC112" s="78"/>
       <c r="AD112" s="78"/>
     </row>
-    <row r="113" spans="1:30">
+    <row r="113" spans="1:30" ht="14">
       <c r="A113" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8472,7 +8482,7 @@
       <c r="AC113" s="32"/>
       <c r="AD113" s="32"/>
     </row>
-    <row r="114" spans="1:30">
+    <row r="114" spans="1:30" ht="14">
       <c r="A114" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8506,7 +8516,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="1:30">
+    <row r="115" spans="1:30" ht="14">
       <c r="A115" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8540,7 +8550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="116" spans="1:30">
+    <row r="116" spans="1:30" ht="14">
       <c r="A116" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8598,7 +8608,7 @@
       <c r="AC116" s="24"/>
       <c r="AD116" s="24"/>
     </row>
-    <row r="117" spans="1:30">
+    <row r="117" spans="1:30" ht="14">
       <c r="A117" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8638,7 +8648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:30">
+    <row r="118" spans="1:30" ht="14">
       <c r="A118" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8696,7 +8706,7 @@
       <c r="AC118" s="24"/>
       <c r="AD118" s="24"/>
     </row>
-    <row r="119" spans="1:30">
+    <row r="119" spans="1:30" ht="14">
       <c r="A119" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8730,7 +8740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:30">
+    <row r="120" spans="1:30" ht="14">
       <c r="A120" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8788,7 +8798,7 @@
       <c r="AC120" s="24"/>
       <c r="AD120" s="24"/>
     </row>
-    <row r="121" spans="1:30">
+    <row r="121" spans="1:30" ht="14">
       <c r="A121" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8846,7 +8856,7 @@
       <c r="AC121" s="24"/>
       <c r="AD121" s="24"/>
     </row>
-    <row r="122" spans="1:30">
+    <row r="122" spans="1:30" ht="14">
       <c r="A122" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8904,7 +8914,7 @@
       <c r="AC122" s="32"/>
       <c r="AD122" s="32"/>
     </row>
-    <row r="123" spans="1:30">
+    <row r="123" spans="1:30" ht="14">
       <c r="A123" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8938,7 +8948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:30">
+    <row r="124" spans="1:30" ht="14">
       <c r="A124" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -8996,7 +9006,7 @@
       <c r="AC124" s="21"/>
       <c r="AD124" s="21"/>
     </row>
-    <row r="125" spans="1:30">
+    <row r="125" spans="1:30" ht="14">
       <c r="A125" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9036,7 +9046,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="1:30">
+    <row r="126" spans="1:30" ht="14">
       <c r="A126" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9070,7 +9080,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:30">
+    <row r="127" spans="1:30" ht="14">
       <c r="A127" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9110,7 +9120,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:30">
+    <row r="128" spans="1:30" ht="14">
       <c r="A128" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9168,7 +9178,7 @@
       <c r="AC128" s="32"/>
       <c r="AD128" s="32"/>
     </row>
-    <row r="129" spans="1:30">
+    <row r="129" spans="1:30" ht="14">
       <c r="A129" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9226,7 +9236,7 @@
       <c r="AC129" s="24"/>
       <c r="AD129" s="24"/>
     </row>
-    <row r="130" spans="1:30">
+    <row r="130" spans="1:30" ht="14">
       <c r="A130" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9260,7 +9270,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:30">
+    <row r="131" spans="1:30" ht="14">
       <c r="A131" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9294,7 +9304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" spans="1:30">
+    <row r="132" spans="1:30" ht="14">
       <c r="A132" s="79" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9337,7 +9347,7 @@
       <c r="N132" s="32"/>
       <c r="O132" s="32"/>
     </row>
-    <row r="133" spans="1:30">
+    <row r="133" spans="1:30" ht="14">
       <c r="A133" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9395,7 +9405,7 @@
       <c r="AC133" s="24"/>
       <c r="AD133" s="24"/>
     </row>
-    <row r="134" spans="1:30">
+    <row r="134" spans="1:30" ht="14">
       <c r="A134" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9429,7 +9439,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" spans="1:30">
+    <row r="135" spans="1:30" ht="14">
       <c r="A135" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9487,7 +9497,7 @@
       <c r="AC135" s="21"/>
       <c r="AD135" s="21"/>
     </row>
-    <row r="136" spans="1:30">
+    <row r="136" spans="1:30" ht="14">
       <c r="A136" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9521,7 +9531,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:30">
+    <row r="137" spans="1:30" ht="14">
       <c r="A137" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9555,7 +9565,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="138" spans="1:30">
+    <row r="138" spans="1:30" ht="14">
       <c r="A138" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9613,7 +9623,7 @@
       <c r="AC138" s="24"/>
       <c r="AD138" s="24"/>
     </row>
-    <row r="139" spans="1:30">
+    <row r="139" spans="1:30" ht="14">
       <c r="A139" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9653,7 +9663,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:30">
+    <row r="140" spans="1:30" ht="14">
       <c r="A140" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9687,7 +9697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:30">
+    <row r="141" spans="1:30" ht="14">
       <c r="A141" s="53" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9745,7 +9755,7 @@
       <c r="AC141" s="21"/>
       <c r="AD141" s="21"/>
     </row>
-    <row r="142" spans="1:30">
+    <row r="142" spans="1:30" ht="14">
       <c r="A142" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9803,7 +9813,7 @@
       <c r="AC142" s="24"/>
       <c r="AD142" s="24"/>
     </row>
-    <row r="143" spans="1:30">
+    <row r="143" spans="1:30" ht="14">
       <c r="A143" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9861,7 +9871,7 @@
       <c r="AC143" s="24"/>
       <c r="AD143" s="24"/>
     </row>
-    <row r="144" spans="1:30">
+    <row r="144" spans="1:30" ht="14">
       <c r="A144" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9895,7 +9905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="1:30">
+    <row r="145" spans="1:30" ht="14">
       <c r="A145" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9929,7 +9939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" spans="1:30">
+    <row r="146" spans="1:30" ht="14">
       <c r="A146" s="6" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#NAME?</v>
@@ -9969,7 +9979,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:30">
+    <row r="147" spans="1:30" ht="14">
       <c r="A147" s="6"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
@@ -9981,7 +9991,7 @@
       <c r="I147" s="81"/>
       <c r="L147" s="13"/>
     </row>
-    <row r="148" spans="1:30">
+    <row r="148" spans="1:30" ht="14">
       <c r="A148" s="6"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
@@ -9993,7 +10003,7 @@
       <c r="I148" s="81"/>
       <c r="L148" s="13"/>
     </row>
-    <row r="149" spans="1:30">
+    <row r="149" spans="1:30" ht="14">
       <c r="A149" s="6"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
@@ -10005,7 +10015,7 @@
       <c r="I149" s="81"/>
       <c r="L149" s="13"/>
     </row>
-    <row r="150" spans="1:30">
+    <row r="150" spans="1:30" ht="14">
       <c r="A150" s="6"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -10017,7 +10027,7 @@
       <c r="I150" s="81"/>
       <c r="L150" s="13"/>
     </row>
-    <row r="151" spans="1:30">
+    <row r="151" spans="1:30" ht="14">
       <c r="A151" s="6" t="e">
         <f t="shared" ref="A151:A158" ca="1" si="2">_xludf.CONCAT(C151," (RS)")</f>
         <v>#NAME?</v>
@@ -10075,7 +10085,7 @@
       <c r="AC151" s="32"/>
       <c r="AD151" s="32"/>
     </row>
-    <row r="152" spans="1:30">
+    <row r="152" spans="1:30" ht="14">
       <c r="A152" s="6" t="e">
         <f t="shared" ca="1" si="2"/>
         <v>#NAME?</v>
@@ -10115,7 +10125,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" spans="1:30">
+    <row r="153" spans="1:30" ht="14">
       <c r="A153" s="6" t="e">
         <f t="shared" ca="1" si="2"/>
         <v>#NAME?</v>
@@ -10173,7 +10183,7 @@
       <c r="AC153" s="32"/>
       <c r="AD153" s="32"/>
     </row>
-    <row r="154" spans="1:30">
+    <row r="154" spans="1:30" ht="14">
       <c r="A154" s="6" t="e">
         <f t="shared" ca="1" si="2"/>
         <v>#NAME?</v>
@@ -10231,7 +10241,7 @@
       <c r="AC154" s="32"/>
       <c r="AD154" s="32"/>
     </row>
-    <row r="155" spans="1:30">
+    <row r="155" spans="1:30" ht="14">
       <c r="A155" s="6" t="e">
         <f t="shared" ca="1" si="2"/>
         <v>#NAME?</v>
@@ -10271,7 +10281,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:30">
+    <row r="156" spans="1:30" ht="14">
       <c r="A156" s="6" t="e">
         <f t="shared" ca="1" si="2"/>
         <v>#NAME?</v>
@@ -10305,7 +10315,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:30">
+    <row r="157" spans="1:30" ht="14">
       <c r="A157" s="6" t="e">
         <f t="shared" ca="1" si="2"/>
         <v>#NAME?</v>
@@ -10363,7 +10373,7 @@
       <c r="AC157" s="24"/>
       <c r="AD157" s="24"/>
     </row>
-    <row r="158" spans="1:30">
+    <row r="158" spans="1:30" ht="14">
       <c r="A158" s="6" t="e">
         <f t="shared" ca="1" si="2"/>
         <v>#NAME?</v>
@@ -10397,7 +10407,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:30">
+    <row r="159" spans="1:30" ht="14">
       <c r="A159" s="6"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
@@ -10409,7 +10419,7 @@
       <c r="I159" s="81"/>
       <c r="L159" s="13"/>
     </row>
-    <row r="160" spans="1:30">
+    <row r="160" spans="1:30" ht="14">
       <c r="A160" s="6" t="e">
         <f t="shared" ref="A160:A414" ca="1" si="4">_xludf.CONCAT(C160," (RS)")</f>
         <v>#NAME?</v>
@@ -10467,7 +10477,7 @@
       <c r="AC160" s="32"/>
       <c r="AD160" s="32"/>
     </row>
-    <row r="161" spans="1:30">
+    <row r="161" spans="1:30" ht="14">
       <c r="A161" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -10525,7 +10535,7 @@
       <c r="AC161" s="32"/>
       <c r="AD161" s="32"/>
     </row>
-    <row r="162" spans="1:30">
+    <row r="162" spans="1:30" ht="14">
       <c r="A162" s="61" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -10583,7 +10593,7 @@
       <c r="AC162" s="69"/>
       <c r="AD162" s="69"/>
     </row>
-    <row r="163" spans="1:30">
+    <row r="163" spans="1:30" ht="14">
       <c r="A163" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -10641,7 +10651,7 @@
       <c r="AC163" s="24"/>
       <c r="AD163" s="24"/>
     </row>
-    <row r="164" spans="1:30">
+    <row r="164" spans="1:30" ht="14">
       <c r="A164" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -10699,7 +10709,7 @@
       <c r="AC164" s="32"/>
       <c r="AD164" s="32"/>
     </row>
-    <row r="165" spans="1:30">
+    <row r="165" spans="1:30" ht="14">
       <c r="A165" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -10733,7 +10743,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:30">
+    <row r="166" spans="1:30" ht="14">
       <c r="A166" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -10767,7 +10777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:30">
+    <row r="167" spans="1:30" ht="14">
       <c r="A167" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -10825,7 +10835,7 @@
       <c r="AC167" s="24"/>
       <c r="AD167" s="24"/>
     </row>
-    <row r="168" spans="1:30">
+    <row r="168" spans="1:30" ht="14">
       <c r="A168" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -10883,7 +10893,7 @@
       <c r="AC168" s="24"/>
       <c r="AD168" s="24"/>
     </row>
-    <row r="169" spans="1:30">
+    <row r="169" spans="1:30" ht="14">
       <c r="A169" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -10923,7 +10933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="170" spans="1:30">
+    <row r="170" spans="1:30" ht="14">
       <c r="A170" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -10963,7 +10973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:30">
+    <row r="171" spans="1:30" ht="14">
       <c r="A171" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11021,7 +11031,7 @@
       <c r="AC171" s="32"/>
       <c r="AD171" s="32"/>
     </row>
-    <row r="172" spans="1:30">
+    <row r="172" spans="1:30" ht="14">
       <c r="A172" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11079,7 +11089,7 @@
       <c r="AC172" s="24"/>
       <c r="AD172" s="24"/>
     </row>
-    <row r="173" spans="1:30">
+    <row r="173" spans="1:30" ht="14">
       <c r="A173" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11137,7 +11147,7 @@
       <c r="AC173" s="24"/>
       <c r="AD173" s="24"/>
     </row>
-    <row r="174" spans="1:30">
+    <row r="174" spans="1:30" ht="14">
       <c r="A174" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11195,7 +11205,7 @@
       <c r="AC174" s="32"/>
       <c r="AD174" s="32"/>
     </row>
-    <row r="175" spans="1:30">
+    <row r="175" spans="1:30" ht="14">
       <c r="A175" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11253,7 +11263,7 @@
       <c r="AC175" s="24"/>
       <c r="AD175" s="24"/>
     </row>
-    <row r="176" spans="1:30">
+    <row r="176" spans="1:30" ht="14">
       <c r="A176" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11287,7 +11297,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="177" spans="1:30">
+    <row r="177" spans="1:30" ht="14">
       <c r="A177" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11345,7 +11355,7 @@
       <c r="AC177" s="32"/>
       <c r="AD177" s="32"/>
     </row>
-    <row r="178" spans="1:30">
+    <row r="178" spans="1:30" ht="14">
       <c r="A178" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11379,7 +11389,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" spans="1:30">
+    <row r="179" spans="1:30" ht="14">
       <c r="A179" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11419,7 +11429,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" spans="1:30">
+    <row r="180" spans="1:30" ht="14">
       <c r="A180" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11477,7 +11487,7 @@
       <c r="AC180" s="24"/>
       <c r="AD180" s="24"/>
     </row>
-    <row r="181" spans="1:30">
+    <row r="181" spans="1:30" ht="14">
       <c r="A181" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11511,7 +11521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="182" spans="1:30">
+    <row r="182" spans="1:30" ht="14">
       <c r="A182" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11569,7 +11579,7 @@
       <c r="AC182" s="32"/>
       <c r="AD182" s="32"/>
     </row>
-    <row r="183" spans="1:30">
+    <row r="183" spans="1:30" ht="14">
       <c r="A183" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11627,7 +11637,7 @@
       <c r="AC183" s="78"/>
       <c r="AD183" s="78"/>
     </row>
-    <row r="184" spans="1:30">
+    <row r="184" spans="1:30" ht="14">
       <c r="A184" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11685,7 +11695,7 @@
       <c r="AC184" s="24"/>
       <c r="AD184" s="24"/>
     </row>
-    <row r="185" spans="1:30">
+    <row r="185" spans="1:30" ht="14">
       <c r="A185" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11743,7 +11753,7 @@
       <c r="AC185" s="32"/>
       <c r="AD185" s="32"/>
     </row>
-    <row r="186" spans="1:30">
+    <row r="186" spans="1:30" ht="14">
       <c r="A186" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11777,7 +11787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="187" spans="1:30">
+    <row r="187" spans="1:30" ht="14">
       <c r="A187" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11835,7 +11845,7 @@
       <c r="AC187" s="24"/>
       <c r="AD187" s="24"/>
     </row>
-    <row r="188" spans="1:30">
+    <row r="188" spans="1:30" ht="14">
       <c r="A188" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11893,7 +11903,7 @@
       <c r="AC188" s="24"/>
       <c r="AD188" s="24"/>
     </row>
-    <row r="189" spans="1:30">
+    <row r="189" spans="1:30" ht="14">
       <c r="A189" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11933,7 +11943,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="190" spans="1:30">
+    <row r="190" spans="1:30" ht="14">
       <c r="A190" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -11967,7 +11977,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:30">
+    <row r="191" spans="1:30" ht="14">
       <c r="A191" s="61" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12025,7 +12035,7 @@
       <c r="AC191" s="69"/>
       <c r="AD191" s="69"/>
     </row>
-    <row r="192" spans="1:30">
+    <row r="192" spans="1:30" ht="14">
       <c r="A192" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12083,7 +12093,7 @@
       <c r="AC192" s="24"/>
       <c r="AD192" s="24"/>
     </row>
-    <row r="193" spans="1:30">
+    <row r="193" spans="1:30" ht="14">
       <c r="A193" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12141,7 +12151,7 @@
       <c r="AC193" s="24"/>
       <c r="AD193" s="24"/>
     </row>
-    <row r="194" spans="1:30">
+    <row r="194" spans="1:30" ht="14">
       <c r="A194" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12199,7 +12209,7 @@
       <c r="AC194" s="24"/>
       <c r="AD194" s="24"/>
     </row>
-    <row r="195" spans="1:30">
+    <row r="195" spans="1:30" ht="14">
       <c r="A195" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12233,7 +12243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" spans="1:30">
+    <row r="196" spans="1:30" ht="14">
       <c r="A196" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12291,7 +12301,7 @@
       <c r="AC196" s="24"/>
       <c r="AD196" s="24"/>
     </row>
-    <row r="197" spans="1:30">
+    <row r="197" spans="1:30" ht="14">
       <c r="A197" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12325,7 +12335,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="198" spans="1:30">
+    <row r="198" spans="1:30" ht="14">
       <c r="A198" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12359,7 +12369,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="1:30">
+    <row r="199" spans="1:30" ht="14">
       <c r="A199" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12393,7 +12403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="200" spans="1:30">
+    <row r="200" spans="1:30" ht="14">
       <c r="A200" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12427,7 +12437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" spans="1:30">
+    <row r="201" spans="1:30" ht="14">
       <c r="A201" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12461,7 +12471,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="202" spans="1:30">
+    <row r="202" spans="1:30" ht="14">
       <c r="A202" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12495,7 +12505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="203" spans="1:30">
+    <row r="203" spans="1:30" ht="14">
       <c r="A203" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12553,7 +12563,7 @@
       <c r="AC203" s="21"/>
       <c r="AD203" s="21"/>
     </row>
-    <row r="204" spans="1:30">
+    <row r="204" spans="1:30" ht="14">
       <c r="A204" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12611,7 +12621,7 @@
       <c r="AC204" s="24"/>
       <c r="AD204" s="24"/>
     </row>
-    <row r="205" spans="1:30">
+    <row r="205" spans="1:30" ht="14">
       <c r="A205" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12669,7 +12679,7 @@
       <c r="AC205" s="24"/>
       <c r="AD205" s="24"/>
     </row>
-    <row r="206" spans="1:30">
+    <row r="206" spans="1:30" ht="14">
       <c r="A206" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12703,7 +12713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="1:30">
+    <row r="207" spans="1:30" ht="14">
       <c r="A207" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12761,7 +12771,7 @@
       <c r="AC207" s="24"/>
       <c r="AD207" s="24"/>
     </row>
-    <row r="208" spans="1:30">
+    <row r="208" spans="1:30" ht="14">
       <c r="A208" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12819,7 +12829,7 @@
       <c r="AC208" s="24"/>
       <c r="AD208" s="24"/>
     </row>
-    <row r="209" spans="1:30">
+    <row r="209" spans="1:30" ht="14">
       <c r="A209" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12877,7 +12887,7 @@
       <c r="AC209" s="24"/>
       <c r="AD209" s="24"/>
     </row>
-    <row r="210" spans="1:30">
+    <row r="210" spans="1:30" ht="14">
       <c r="A210" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12935,7 +12945,7 @@
       <c r="AC210" s="21"/>
       <c r="AD210" s="21"/>
     </row>
-    <row r="211" spans="1:30">
+    <row r="211" spans="1:30" ht="14">
       <c r="A211" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -12993,7 +13003,7 @@
       <c r="AC211" s="32"/>
       <c r="AD211" s="32"/>
     </row>
-    <row r="212" spans="1:30">
+    <row r="212" spans="1:30" ht="14">
       <c r="A212" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13027,7 +13037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="213" spans="1:30">
+    <row r="213" spans="1:30" ht="14">
       <c r="A213" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13061,7 +13071,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="1:30">
+    <row r="214" spans="1:30" ht="14">
       <c r="A214" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13119,7 +13129,7 @@
       <c r="AC214" s="24"/>
       <c r="AD214" s="24"/>
     </row>
-    <row r="215" spans="1:30">
+    <row r="215" spans="1:30" ht="14">
       <c r="A215" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13159,7 +13169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="216" spans="1:30">
+    <row r="216" spans="1:30" ht="14">
       <c r="A216" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13193,7 +13203,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="217" spans="1:30">
+    <row r="217" spans="1:30" ht="14">
       <c r="A217" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13233,7 +13243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="218" spans="1:30">
+    <row r="218" spans="1:30" ht="14">
       <c r="A218" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13267,7 +13277,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="219" spans="1:30">
+    <row r="219" spans="1:30" ht="14">
       <c r="A219" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13325,7 +13335,7 @@
       <c r="AC219" s="24"/>
       <c r="AD219" s="24"/>
     </row>
-    <row r="220" spans="1:30">
+    <row r="220" spans="1:30" ht="14">
       <c r="A220" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13359,7 +13369,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="221" spans="1:30">
+    <row r="221" spans="1:30" ht="14">
       <c r="A221" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13417,7 +13427,7 @@
       <c r="AC221" s="21"/>
       <c r="AD221" s="21"/>
     </row>
-    <row r="222" spans="1:30">
+    <row r="222" spans="1:30" ht="14">
       <c r="A222" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13457,7 +13467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="1:30">
+    <row r="223" spans="1:30" ht="14">
       <c r="A223" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13491,7 +13501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="224" spans="1:30">
+    <row r="224" spans="1:30" ht="14">
       <c r="A224" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13549,7 +13559,7 @@
       <c r="AC224" s="24"/>
       <c r="AD224" s="24"/>
     </row>
-    <row r="225" spans="1:30">
+    <row r="225" spans="1:30" ht="14">
       <c r="A225" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13583,7 +13593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="1:30">
+    <row r="226" spans="1:30" ht="14">
       <c r="A226" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13617,7 +13627,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="227" spans="1:30">
+    <row r="227" spans="1:30" ht="14">
       <c r="A227" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13657,7 +13667,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="228" spans="1:30">
+    <row r="228" spans="1:30" ht="14">
       <c r="A228" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13715,7 +13725,7 @@
       <c r="AC228" s="24"/>
       <c r="AD228" s="24"/>
     </row>
-    <row r="229" spans="1:30">
+    <row r="229" spans="1:30" ht="14">
       <c r="A229" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13755,7 +13765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" spans="1:30">
+    <row r="230" spans="1:30" ht="14">
       <c r="A230" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13813,7 +13823,7 @@
       <c r="AC230" s="24"/>
       <c r="AD230" s="24"/>
     </row>
-    <row r="231" spans="1:30">
+    <row r="231" spans="1:30" ht="14">
       <c r="A231" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13847,7 +13857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="232" spans="1:30">
+    <row r="232" spans="1:30" ht="14">
       <c r="A232" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13881,7 +13891,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="233" spans="1:30">
+    <row r="233" spans="1:30" ht="14">
       <c r="A233" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13915,7 +13925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="234" spans="1:30">
+    <row r="234" spans="1:30" ht="14">
       <c r="A234" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -13949,7 +13959,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" spans="1:30">
+    <row r="235" spans="1:30" ht="14">
       <c r="A235" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14007,7 +14017,7 @@
       <c r="AC235" s="78"/>
       <c r="AD235" s="78"/>
     </row>
-    <row r="236" spans="1:30">
+    <row r="236" spans="1:30" ht="14">
       <c r="A236" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14065,7 +14075,7 @@
       <c r="AC236" s="24"/>
       <c r="AD236" s="24"/>
     </row>
-    <row r="237" spans="1:30">
+    <row r="237" spans="1:30" ht="14">
       <c r="A237" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14099,7 +14109,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="1:30">
+    <row r="238" spans="1:30" ht="14">
       <c r="A238" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14157,7 +14167,7 @@
       <c r="AC238" s="32"/>
       <c r="AD238" s="32"/>
     </row>
-    <row r="239" spans="1:30">
+    <row r="239" spans="1:30" ht="14">
       <c r="A239" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14191,7 +14201,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="240" spans="1:30">
+    <row r="240" spans="1:30" ht="14">
       <c r="A240" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14225,7 +14235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="241" spans="1:30">
+    <row r="241" spans="1:30" ht="14">
       <c r="A241" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14265,7 +14275,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" spans="1:30">
+    <row r="242" spans="1:30" ht="14">
       <c r="A242" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14323,7 +14333,7 @@
       <c r="AC242" s="21"/>
       <c r="AD242" s="21"/>
     </row>
-    <row r="243" spans="1:30">
+    <row r="243" spans="1:30" ht="14">
       <c r="A243" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14381,7 +14391,7 @@
       <c r="AC243" s="24"/>
       <c r="AD243" s="24"/>
     </row>
-    <row r="244" spans="1:30">
+    <row r="244" spans="1:30" ht="14">
       <c r="A244" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14415,7 +14425,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" spans="1:30">
+    <row r="245" spans="1:30" ht="14">
       <c r="A245" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14473,7 +14483,7 @@
       <c r="AC245" s="24"/>
       <c r="AD245" s="24"/>
     </row>
-    <row r="246" spans="1:30">
+    <row r="246" spans="1:30" ht="14">
       <c r="A246" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14531,7 +14541,7 @@
       <c r="AC246" s="21"/>
       <c r="AD246" s="21"/>
     </row>
-    <row r="247" spans="1:30">
+    <row r="247" spans="1:30" ht="14">
       <c r="A247" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14565,7 +14575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="248" spans="1:30">
+    <row r="248" spans="1:30" ht="14">
       <c r="A248" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14623,7 +14633,7 @@
       <c r="AC248" s="24"/>
       <c r="AD248" s="24"/>
     </row>
-    <row r="249" spans="1:30">
+    <row r="249" spans="1:30" ht="14">
       <c r="A249" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14681,7 +14691,7 @@
       <c r="AC249" s="24"/>
       <c r="AD249" s="24"/>
     </row>
-    <row r="250" spans="1:30">
+    <row r="250" spans="1:30" ht="14">
       <c r="A250" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14739,7 +14749,7 @@
       <c r="AC250" s="24"/>
       <c r="AD250" s="24"/>
     </row>
-    <row r="251" spans="1:30">
+    <row r="251" spans="1:30" ht="14">
       <c r="A251" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14797,7 +14807,7 @@
       <c r="AC251" s="32"/>
       <c r="AD251" s="32"/>
     </row>
-    <row r="252" spans="1:30">
+    <row r="252" spans="1:30" ht="14">
       <c r="A252" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14855,7 +14865,7 @@
       <c r="AC252" s="21"/>
       <c r="AD252" s="21"/>
     </row>
-    <row r="253" spans="1:30">
+    <row r="253" spans="1:30" ht="14">
       <c r="A253" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14913,7 +14923,7 @@
       <c r="AC253" s="32"/>
       <c r="AD253" s="32"/>
     </row>
-    <row r="254" spans="1:30">
+    <row r="254" spans="1:30" ht="14">
       <c r="A254" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -14971,7 +14981,7 @@
       <c r="AC254" s="24"/>
       <c r="AD254" s="24"/>
     </row>
-    <row r="255" spans="1:30">
+    <row r="255" spans="1:30" ht="14">
       <c r="A255" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15011,7 +15021,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="256" spans="1:30">
+    <row r="256" spans="1:30" ht="14">
       <c r="A256" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15069,7 +15079,7 @@
       <c r="AC256" s="32"/>
       <c r="AD256" s="32"/>
     </row>
-    <row r="257" spans="1:30">
+    <row r="257" spans="1:30" ht="14">
       <c r="A257" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15127,7 +15137,7 @@
       <c r="AC257" s="78"/>
       <c r="AD257" s="78"/>
     </row>
-    <row r="258" spans="1:30">
+    <row r="258" spans="1:30" ht="14">
       <c r="A258" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15185,7 +15195,7 @@
       <c r="AC258" s="21"/>
       <c r="AD258" s="21"/>
     </row>
-    <row r="259" spans="1:30">
+    <row r="259" spans="1:30" ht="14">
       <c r="A259" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15243,7 +15253,7 @@
       <c r="AC259" s="24"/>
       <c r="AD259" s="24"/>
     </row>
-    <row r="260" spans="1:30">
+    <row r="260" spans="1:30" ht="14">
       <c r="A260" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15277,7 +15287,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="261" spans="1:30">
+    <row r="261" spans="1:30" ht="14">
       <c r="A261" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15311,7 +15321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="262" spans="1:30">
+    <row r="262" spans="1:30" ht="14">
       <c r="A262" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15369,7 +15379,7 @@
       <c r="AC262" s="24"/>
       <c r="AD262" s="24"/>
     </row>
-    <row r="263" spans="1:30">
+    <row r="263" spans="1:30" ht="14">
       <c r="A263" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15427,7 +15437,7 @@
       <c r="AC263" s="24"/>
       <c r="AD263" s="24"/>
     </row>
-    <row r="264" spans="1:30">
+    <row r="264" spans="1:30" ht="14">
       <c r="A264" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15485,7 +15495,7 @@
       <c r="AC264" s="24"/>
       <c r="AD264" s="24"/>
     </row>
-    <row r="265" spans="1:30">
+    <row r="265" spans="1:30" ht="14">
       <c r="A265" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15543,7 +15553,7 @@
       <c r="AC265" s="24"/>
       <c r="AD265" s="24"/>
     </row>
-    <row r="266" spans="1:30">
+    <row r="266" spans="1:30" ht="14">
       <c r="A266" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15601,7 +15611,7 @@
       <c r="AC266" s="78"/>
       <c r="AD266" s="78"/>
     </row>
-    <row r="267" spans="1:30">
+    <row r="267" spans="1:30" ht="14">
       <c r="A267" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15659,7 +15669,7 @@
       <c r="AC267" s="24"/>
       <c r="AD267" s="24"/>
     </row>
-    <row r="268" spans="1:30">
+    <row r="268" spans="1:30" ht="14">
       <c r="A268" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15693,7 +15703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="269" spans="1:30">
+    <row r="269" spans="1:30" ht="14">
       <c r="A269" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15751,7 +15761,7 @@
       <c r="AC269" s="24"/>
       <c r="AD269" s="24"/>
     </row>
-    <row r="270" spans="1:30">
+    <row r="270" spans="1:30" ht="14">
       <c r="A270" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15809,7 +15819,7 @@
       <c r="AC270" s="24"/>
       <c r="AD270" s="24"/>
     </row>
-    <row r="271" spans="1:30">
+    <row r="271" spans="1:30" ht="14">
       <c r="A271" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15867,7 +15877,7 @@
       <c r="AC271" s="21"/>
       <c r="AD271" s="21"/>
     </row>
-    <row r="272" spans="1:30">
+    <row r="272" spans="1:30" ht="14">
       <c r="A272" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15925,7 +15935,7 @@
       <c r="AC272" s="21"/>
       <c r="AD272" s="21"/>
     </row>
-    <row r="273" spans="1:30">
+    <row r="273" spans="1:30" ht="14">
       <c r="A273" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -15983,7 +15993,7 @@
       <c r="AC273" s="24"/>
       <c r="AD273" s="24"/>
     </row>
-    <row r="274" spans="1:30">
+    <row r="274" spans="1:30" ht="14">
       <c r="A274" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16041,7 +16051,7 @@
       <c r="AC274" s="21"/>
       <c r="AD274" s="21"/>
     </row>
-    <row r="275" spans="1:30">
+    <row r="275" spans="1:30" ht="14">
       <c r="A275" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16099,7 +16109,7 @@
       <c r="AC275" s="24"/>
       <c r="AD275" s="24"/>
     </row>
-    <row r="276" spans="1:30">
+    <row r="276" spans="1:30" ht="14">
       <c r="A276" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16139,7 +16149,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="277" spans="1:30">
+    <row r="277" spans="1:30" ht="14">
       <c r="A277" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16197,7 +16207,7 @@
       <c r="AC277" s="24"/>
       <c r="AD277" s="24"/>
     </row>
-    <row r="278" spans="1:30">
+    <row r="278" spans="1:30" ht="14">
       <c r="A278" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16255,7 +16265,7 @@
       <c r="AC278" s="24"/>
       <c r="AD278" s="24"/>
     </row>
-    <row r="279" spans="1:30">
+    <row r="279" spans="1:30" ht="14">
       <c r="A279" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16313,7 +16323,7 @@
       <c r="AC279" s="24"/>
       <c r="AD279" s="24"/>
     </row>
-    <row r="280" spans="1:30">
+    <row r="280" spans="1:30" ht="14">
       <c r="A280" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16347,7 +16357,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="281" spans="1:30">
+    <row r="281" spans="1:30" ht="14">
       <c r="A281" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16405,7 +16415,7 @@
       <c r="AC281" s="24"/>
       <c r="AD281" s="24"/>
     </row>
-    <row r="282" spans="1:30">
+    <row r="282" spans="1:30" ht="14">
       <c r="A282" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16439,7 +16449,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="283" spans="1:30">
+    <row r="283" spans="1:30" ht="14">
       <c r="A283" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16473,7 +16483,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="284" spans="1:30">
+    <row r="284" spans="1:30" ht="14">
       <c r="A284" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16531,7 +16541,7 @@
       <c r="AC284" s="24"/>
       <c r="AD284" s="24"/>
     </row>
-    <row r="285" spans="1:30">
+    <row r="285" spans="1:30" ht="14">
       <c r="A285" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16589,7 +16599,7 @@
       <c r="AC285" s="24"/>
       <c r="AD285" s="24"/>
     </row>
-    <row r="286" spans="1:30">
+    <row r="286" spans="1:30" ht="14">
       <c r="A286" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16623,7 +16633,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="287" spans="1:30">
+    <row r="287" spans="1:30" ht="14">
       <c r="A287" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16681,7 +16691,7 @@
       <c r="AC287" s="24"/>
       <c r="AD287" s="24"/>
     </row>
-    <row r="288" spans="1:30">
+    <row r="288" spans="1:30" ht="14">
       <c r="A288" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16739,7 +16749,7 @@
       <c r="AC288" s="24"/>
       <c r="AD288" s="24"/>
     </row>
-    <row r="289" spans="1:30">
+    <row r="289" spans="1:30" ht="14">
       <c r="A289" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16773,7 +16783,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="290" spans="1:30">
+    <row r="290" spans="1:30" ht="14">
       <c r="A290" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16831,7 +16841,7 @@
       <c r="AC290" s="24"/>
       <c r="AD290" s="24"/>
     </row>
-    <row r="291" spans="1:30">
+    <row r="291" spans="1:30" ht="14">
       <c r="A291" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16889,7 +16899,7 @@
       <c r="AC291" s="24"/>
       <c r="AD291" s="24"/>
     </row>
-    <row r="292" spans="1:30">
+    <row r="292" spans="1:30" ht="14">
       <c r="A292" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16923,7 +16933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="293" spans="1:30">
+    <row r="293" spans="1:30" ht="14">
       <c r="A293" s="79" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -16981,7 +16991,7 @@
       <c r="AC293" s="32"/>
       <c r="AD293" s="32"/>
     </row>
-    <row r="294" spans="1:30">
+    <row r="294" spans="1:30" ht="14">
       <c r="A294" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17039,7 +17049,7 @@
       <c r="AC294" s="24"/>
       <c r="AD294" s="24"/>
     </row>
-    <row r="295" spans="1:30">
+    <row r="295" spans="1:30" ht="14">
       <c r="A295" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17073,7 +17083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="1:30">
+    <row r="296" spans="1:30" ht="14">
       <c r="A296" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17107,7 +17117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:30">
+    <row r="297" spans="1:30" ht="14">
       <c r="A297" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17141,7 +17151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:30">
+    <row r="298" spans="1:30" ht="14">
       <c r="A298" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17199,7 +17209,7 @@
       <c r="AC298" s="21"/>
       <c r="AD298" s="21"/>
     </row>
-    <row r="299" spans="1:30">
+    <row r="299" spans="1:30" ht="14">
       <c r="A299" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17257,7 +17267,7 @@
       <c r="AC299" s="24"/>
       <c r="AD299" s="24"/>
     </row>
-    <row r="300" spans="1:30">
+    <row r="300" spans="1:30" ht="14">
       <c r="A300" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17315,7 +17325,7 @@
       <c r="AC300" s="24"/>
       <c r="AD300" s="24"/>
     </row>
-    <row r="301" spans="1:30">
+    <row r="301" spans="1:30" ht="14">
       <c r="A301" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17349,7 +17359,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="302" spans="1:30">
+    <row r="302" spans="1:30" ht="14">
       <c r="A302" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17383,7 +17393,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="303" spans="1:30">
+    <row r="303" spans="1:30" ht="14">
       <c r="A303" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17441,7 +17451,7 @@
       <c r="AC303" s="24"/>
       <c r="AD303" s="24"/>
     </row>
-    <row r="304" spans="1:30">
+    <row r="304" spans="1:30" ht="14">
       <c r="A304" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17475,7 +17485,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="305" spans="1:30">
+    <row r="305" spans="1:30" ht="14">
       <c r="A305" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17533,7 +17543,7 @@
       <c r="AC305" s="24"/>
       <c r="AD305" s="24"/>
     </row>
-    <row r="306" spans="1:30">
+    <row r="306" spans="1:30" ht="14">
       <c r="A306" s="79" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17591,7 +17601,7 @@
       <c r="AC306" s="32"/>
       <c r="AD306" s="32"/>
     </row>
-    <row r="307" spans="1:30">
+    <row r="307" spans="1:30" ht="14">
       <c r="A307" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17649,7 +17659,7 @@
       <c r="AC307" s="24"/>
       <c r="AD307" s="24"/>
     </row>
-    <row r="308" spans="1:30">
+    <row r="308" spans="1:30" ht="14">
       <c r="A308" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17707,7 +17717,7 @@
       <c r="AC308" s="24"/>
       <c r="AD308" s="24"/>
     </row>
-    <row r="309" spans="1:30">
+    <row r="309" spans="1:30" ht="14">
       <c r="A309" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17741,7 +17751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="310" spans="1:30">
+    <row r="310" spans="1:30" ht="14">
       <c r="A310" s="79" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17799,7 +17809,7 @@
       <c r="AC310" s="32"/>
       <c r="AD310" s="32"/>
     </row>
-    <row r="311" spans="1:30">
+    <row r="311" spans="1:30" ht="14">
       <c r="A311" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17857,7 +17867,7 @@
       <c r="AC311" s="32"/>
       <c r="AD311" s="32"/>
     </row>
-    <row r="312" spans="1:30">
+    <row r="312" spans="1:30" ht="14">
       <c r="A312" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17897,7 +17907,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="313" spans="1:30">
+    <row r="313" spans="1:30" ht="14">
       <c r="A313" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17955,7 +17965,7 @@
       <c r="AC313" s="24"/>
       <c r="AD313" s="24"/>
     </row>
-    <row r="314" spans="1:30">
+    <row r="314" spans="1:30" ht="14">
       <c r="A314" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -17989,7 +17999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="315" spans="1:30">
+    <row r="315" spans="1:30" ht="14">
       <c r="A315" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18047,7 +18057,7 @@
       <c r="AC315" s="24"/>
       <c r="AD315" s="24"/>
     </row>
-    <row r="316" spans="1:30">
+    <row r="316" spans="1:30" ht="14">
       <c r="A316" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18105,7 +18115,7 @@
       <c r="AC316" s="24"/>
       <c r="AD316" s="24"/>
     </row>
-    <row r="317" spans="1:30">
+    <row r="317" spans="1:30" ht="14">
       <c r="A317" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18163,7 +18173,7 @@
       <c r="AC317" s="24"/>
       <c r="AD317" s="24"/>
     </row>
-    <row r="318" spans="1:30">
+    <row r="318" spans="1:30" ht="14">
       <c r="A318" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18221,7 +18231,7 @@
       <c r="AC318" s="24"/>
       <c r="AD318" s="24"/>
     </row>
-    <row r="319" spans="1:30">
+    <row r="319" spans="1:30" ht="14">
       <c r="A319" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18261,7 +18271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="320" spans="1:30">
+    <row r="320" spans="1:30" ht="14">
       <c r="A320" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18319,7 +18329,7 @@
       <c r="AC320" s="21"/>
       <c r="AD320" s="21"/>
     </row>
-    <row r="321" spans="1:30">
+    <row r="321" spans="1:30" ht="14">
       <c r="A321" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18353,7 +18363,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="322" spans="1:30">
+    <row r="322" spans="1:30" ht="14">
       <c r="A322" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18387,7 +18397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="323" spans="1:30">
+    <row r="323" spans="1:30" ht="14">
       <c r="A323" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18421,7 +18431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="324" spans="1:30">
+    <row r="324" spans="1:30" ht="14">
       <c r="A324" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18479,7 +18489,7 @@
       <c r="AC324" s="24"/>
       <c r="AD324" s="24"/>
     </row>
-    <row r="325" spans="1:30">
+    <row r="325" spans="1:30" ht="14">
       <c r="A325" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18513,7 +18523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="326" spans="1:30">
+    <row r="326" spans="1:30" ht="14">
       <c r="A326" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18547,7 +18557,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="327" spans="1:30">
+    <row r="327" spans="1:30" ht="14">
       <c r="A327" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18587,7 +18597,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="328" spans="1:30">
+    <row r="328" spans="1:30" ht="14">
       <c r="A328" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18645,7 +18655,7 @@
       <c r="AC328" s="78"/>
       <c r="AD328" s="78"/>
     </row>
-    <row r="329" spans="1:30">
+    <row r="329" spans="1:30" ht="14">
       <c r="A329" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18685,7 +18695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="330" spans="1:30">
+    <row r="330" spans="1:30" ht="14">
       <c r="A330" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18725,7 +18735,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="331" spans="1:30">
+    <row r="331" spans="1:30" ht="14">
       <c r="A331" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18783,7 +18793,7 @@
       <c r="AC331" s="21"/>
       <c r="AD331" s="21"/>
     </row>
-    <row r="332" spans="1:30">
+    <row r="332" spans="1:30" ht="14">
       <c r="A332" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18841,7 +18851,7 @@
       <c r="AC332" s="24"/>
       <c r="AD332" s="24"/>
     </row>
-    <row r="333" spans="1:30">
+    <row r="333" spans="1:30" ht="14">
       <c r="A333" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18875,7 +18885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="334" spans="1:30">
+    <row r="334" spans="1:30" ht="14">
       <c r="A334" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18909,7 +18919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="335" spans="1:30">
+    <row r="335" spans="1:30" ht="14">
       <c r="A335" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18943,7 +18953,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" spans="1:30">
+    <row r="336" spans="1:30" ht="14">
       <c r="A336" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -18977,7 +18987,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="337" spans="1:30">
+    <row r="337" spans="1:30" ht="14">
       <c r="A337" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19035,7 +19045,7 @@
       <c r="AC337" s="32"/>
       <c r="AD337" s="32"/>
     </row>
-    <row r="338" spans="1:30">
+    <row r="338" spans="1:30" ht="14">
       <c r="A338" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19093,7 +19103,7 @@
       <c r="AC338" s="24"/>
       <c r="AD338" s="24"/>
     </row>
-    <row r="339" spans="1:30">
+    <row r="339" spans="1:30" ht="14">
       <c r="A339" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19151,7 +19161,7 @@
       <c r="AC339" s="32"/>
       <c r="AD339" s="32"/>
     </row>
-    <row r="340" spans="1:30">
+    <row r="340" spans="1:30" ht="14">
       <c r="A340" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19209,7 +19219,7 @@
       <c r="AC340" s="24"/>
       <c r="AD340" s="24"/>
     </row>
-    <row r="341" spans="1:30">
+    <row r="341" spans="1:30" ht="14">
       <c r="A341" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19267,7 +19277,7 @@
       <c r="AC341" s="24"/>
       <c r="AD341" s="24"/>
     </row>
-    <row r="342" spans="1:30">
+    <row r="342" spans="1:30" ht="14">
       <c r="A342" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19301,7 +19311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="343" spans="1:30">
+    <row r="343" spans="1:30" ht="14">
       <c r="A343" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19341,7 +19351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="344" spans="1:30">
+    <row r="344" spans="1:30" ht="14">
       <c r="A344" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19375,7 +19385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="345" spans="1:30">
+    <row r="345" spans="1:30" ht="14">
       <c r="A345" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19409,7 +19419,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="346" spans="1:30">
+    <row r="346" spans="1:30" ht="14">
       <c r="A346" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19443,7 +19453,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="347" spans="1:30">
+    <row r="347" spans="1:30" ht="14">
       <c r="A347" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19501,7 +19511,7 @@
       <c r="AC347" s="24"/>
       <c r="AD347" s="24"/>
     </row>
-    <row r="348" spans="1:30">
+    <row r="348" spans="1:30" ht="14">
       <c r="A348" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19535,7 +19545,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="349" spans="1:30">
+    <row r="349" spans="1:30" ht="14">
       <c r="A349" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19575,7 +19585,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="350" spans="1:30">
+    <row r="350" spans="1:30" ht="14">
       <c r="A350" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19633,7 +19643,7 @@
       <c r="AC350" s="24"/>
       <c r="AD350" s="24"/>
     </row>
-    <row r="351" spans="1:30">
+    <row r="351" spans="1:30" ht="14">
       <c r="A351" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19667,7 +19677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="352" spans="1:30">
+    <row r="352" spans="1:30" ht="14">
       <c r="A352" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19725,7 +19735,7 @@
       <c r="AC352" s="24"/>
       <c r="AD352" s="24"/>
     </row>
-    <row r="353" spans="1:30">
+    <row r="353" spans="1:30" ht="14">
       <c r="A353" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19783,7 +19793,7 @@
       <c r="AC353" s="24"/>
       <c r="AD353" s="24"/>
     </row>
-    <row r="354" spans="1:30">
+    <row r="354" spans="1:30" ht="14">
       <c r="A354" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19823,7 +19833,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="355" spans="1:30">
+    <row r="355" spans="1:30" ht="14">
       <c r="A355" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19881,7 +19891,7 @@
       <c r="AC355" s="24"/>
       <c r="AD355" s="24"/>
     </row>
-    <row r="356" spans="1:30">
+    <row r="356" spans="1:30" ht="14">
       <c r="A356" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19939,7 +19949,7 @@
       <c r="AC356" s="24"/>
       <c r="AD356" s="24"/>
     </row>
-    <row r="357" spans="1:30">
+    <row r="357" spans="1:30" ht="14">
       <c r="A357" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -19979,7 +19989,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="358" spans="1:30">
+    <row r="358" spans="1:30" ht="14">
       <c r="A358" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20019,7 +20029,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="359" spans="1:30">
+    <row r="359" spans="1:30" ht="14">
       <c r="A359" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20073,7 +20083,7 @@
       <c r="AC359" s="90"/>
       <c r="AD359" s="90"/>
     </row>
-    <row r="360" spans="1:30">
+    <row r="360" spans="1:30" ht="14">
       <c r="A360" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20107,7 +20117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="361" spans="1:30">
+    <row r="361" spans="1:30" ht="14">
       <c r="A361" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20141,7 +20151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="362" spans="1:30">
+    <row r="362" spans="1:30" ht="14">
       <c r="A362" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20199,7 +20209,7 @@
       <c r="AC362" s="24"/>
       <c r="AD362" s="24"/>
     </row>
-    <row r="363" spans="1:30">
+    <row r="363" spans="1:30" ht="14">
       <c r="A363" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20233,7 +20243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="364" spans="1:30">
+    <row r="364" spans="1:30" ht="14">
       <c r="A364" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20267,7 +20277,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="365" spans="1:30">
+    <row r="365" spans="1:30" ht="14">
       <c r="A365" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20325,7 +20335,7 @@
       <c r="AC365" s="24"/>
       <c r="AD365" s="24"/>
     </row>
-    <row r="366" spans="1:30">
+    <row r="366" spans="1:30" ht="14">
       <c r="A366" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20383,7 +20393,7 @@
       <c r="AC366" s="24"/>
       <c r="AD366" s="24"/>
     </row>
-    <row r="367" spans="1:30">
+    <row r="367" spans="1:30" ht="14">
       <c r="A367" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20441,7 +20451,7 @@
       <c r="AC367" s="24"/>
       <c r="AD367" s="24"/>
     </row>
-    <row r="368" spans="1:30">
+    <row r="368" spans="1:30" ht="14">
       <c r="A368" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20499,7 +20509,7 @@
       <c r="AC368" s="24"/>
       <c r="AD368" s="24"/>
     </row>
-    <row r="369" spans="1:30">
+    <row r="369" spans="1:30" ht="14">
       <c r="A369" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20557,7 +20567,7 @@
       <c r="AC369" s="32"/>
       <c r="AD369" s="32"/>
     </row>
-    <row r="370" spans="1:30">
+    <row r="370" spans="1:30" ht="14">
       <c r="A370" s="79" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20615,7 +20625,7 @@
       <c r="AC370" s="32"/>
       <c r="AD370" s="32"/>
     </row>
-    <row r="371" spans="1:30">
+    <row r="371" spans="1:30" ht="14">
       <c r="A371" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20649,7 +20659,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="372" spans="1:30">
+    <row r="372" spans="1:30" ht="14">
       <c r="A372" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20689,7 +20699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="373" spans="1:30">
+    <row r="373" spans="1:30" ht="14">
       <c r="A373" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20747,7 +20757,7 @@
       <c r="AC373" s="24"/>
       <c r="AD373" s="24"/>
     </row>
-    <row r="374" spans="1:30">
+    <row r="374" spans="1:30" ht="14">
       <c r="A374" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20781,7 +20791,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="375" spans="1:30">
+    <row r="375" spans="1:30" ht="14">
       <c r="A375" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20839,7 +20849,7 @@
       <c r="AC375" s="24"/>
       <c r="AD375" s="24"/>
     </row>
-    <row r="376" spans="1:30">
+    <row r="376" spans="1:30" ht="14">
       <c r="A376" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20873,7 +20883,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="377" spans="1:30">
+    <row r="377" spans="1:30" ht="14">
       <c r="A377" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20907,7 +20917,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="378" spans="1:30">
+    <row r="378" spans="1:30" ht="14">
       <c r="A378" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20941,7 +20951,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="379" spans="1:30">
+    <row r="379" spans="1:30" ht="14">
       <c r="A379" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -20975,7 +20985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="380" spans="1:30">
+    <row r="380" spans="1:30" ht="14">
       <c r="A380" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21033,7 +21043,7 @@
       <c r="AC380" s="24"/>
       <c r="AD380" s="24"/>
     </row>
-    <row r="381" spans="1:30">
+    <row r="381" spans="1:30" ht="14">
       <c r="A381" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21091,7 +21101,7 @@
       <c r="AC381" s="24"/>
       <c r="AD381" s="24"/>
     </row>
-    <row r="382" spans="1:30">
+    <row r="382" spans="1:30" ht="14">
       <c r="A382" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21125,7 +21135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="383" spans="1:30">
+    <row r="383" spans="1:30" ht="14">
       <c r="A383" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21183,7 +21193,7 @@
       <c r="AC383" s="21"/>
       <c r="AD383" s="21"/>
     </row>
-    <row r="384" spans="1:30">
+    <row r="384" spans="1:30" ht="14">
       <c r="A384" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21241,7 +21251,7 @@
       <c r="AC384" s="32"/>
       <c r="AD384" s="32"/>
     </row>
-    <row r="385" spans="1:30">
+    <row r="385" spans="1:30" ht="14">
       <c r="A385" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21275,7 +21285,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="386" spans="1:30">
+    <row r="386" spans="1:30" ht="14">
       <c r="A386" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21309,7 +21319,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="387" spans="1:30">
+    <row r="387" spans="1:30" ht="14">
       <c r="A387" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21367,7 +21377,7 @@
       <c r="AC387" s="21"/>
       <c r="AD387" s="21"/>
     </row>
-    <row r="388" spans="1:30">
+    <row r="388" spans="1:30" ht="14">
       <c r="A388" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21401,7 +21411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="389" spans="1:30">
+    <row r="389" spans="1:30" ht="14">
       <c r="A389" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21459,7 +21469,7 @@
       <c r="AC389" s="24"/>
       <c r="AD389" s="24"/>
     </row>
-    <row r="390" spans="1:30">
+    <row r="390" spans="1:30" ht="14">
       <c r="A390" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21493,7 +21503,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="391" spans="1:30">
+    <row r="391" spans="1:30" ht="14">
       <c r="A391" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21551,7 +21561,7 @@
       <c r="AC391" s="24"/>
       <c r="AD391" s="24"/>
     </row>
-    <row r="392" spans="1:30">
+    <row r="392" spans="1:30" ht="14">
       <c r="A392" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21585,7 +21595,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="393" spans="1:30">
+    <row r="393" spans="1:30" ht="14">
       <c r="A393" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21643,7 +21653,7 @@
       <c r="AC393" s="32"/>
       <c r="AD393" s="32"/>
     </row>
-    <row r="394" spans="1:30">
+    <row r="394" spans="1:30" ht="14">
       <c r="A394" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21701,7 +21711,7 @@
       <c r="AC394" s="24"/>
       <c r="AD394" s="24"/>
     </row>
-    <row r="395" spans="1:30">
+    <row r="395" spans="1:30" ht="14">
       <c r="A395" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21741,7 +21751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="396" spans="1:30">
+    <row r="396" spans="1:30" ht="14">
       <c r="A396" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21799,7 +21809,7 @@
       <c r="AC396" s="21"/>
       <c r="AD396" s="21"/>
     </row>
-    <row r="397" spans="1:30">
+    <row r="397" spans="1:30" ht="14">
       <c r="A397" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21833,7 +21843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="398" spans="1:30">
+    <row r="398" spans="1:30" ht="14">
       <c r="A398" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21891,7 +21901,7 @@
       <c r="AC398" s="24"/>
       <c r="AD398" s="24"/>
     </row>
-    <row r="399" spans="1:30">
+    <row r="399" spans="1:30" ht="14">
       <c r="A399" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21949,7 +21959,7 @@
       <c r="AC399" s="24"/>
       <c r="AD399" s="24"/>
     </row>
-    <row r="400" spans="1:30">
+    <row r="400" spans="1:30" ht="14">
       <c r="A400" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -21983,7 +21993,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="401" spans="1:30">
+    <row r="401" spans="1:30" ht="14">
       <c r="A401" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22041,7 +22051,7 @@
       <c r="AC401" s="24"/>
       <c r="AD401" s="24"/>
     </row>
-    <row r="402" spans="1:30">
+    <row r="402" spans="1:30" ht="14">
       <c r="A402" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22099,7 +22109,7 @@
       <c r="AC402" s="24"/>
       <c r="AD402" s="24"/>
     </row>
-    <row r="403" spans="1:30">
+    <row r="403" spans="1:30" ht="14">
       <c r="A403" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22157,7 +22167,7 @@
       <c r="AC403" s="24"/>
       <c r="AD403" s="24"/>
     </row>
-    <row r="404" spans="1:30">
+    <row r="404" spans="1:30" ht="14">
       <c r="A404" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22215,7 +22225,7 @@
       <c r="AC404" s="24"/>
       <c r="AD404" s="24"/>
     </row>
-    <row r="405" spans="1:30">
+    <row r="405" spans="1:30" ht="14">
       <c r="A405" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22273,7 +22283,7 @@
       <c r="AC405" s="24"/>
       <c r="AD405" s="24"/>
     </row>
-    <row r="406" spans="1:30">
+    <row r="406" spans="1:30" ht="14">
       <c r="A406" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22331,7 +22341,7 @@
       <c r="AC406" s="24"/>
       <c r="AD406" s="24"/>
     </row>
-    <row r="407" spans="1:30">
+    <row r="407" spans="1:30" ht="14">
       <c r="A407" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22389,7 +22399,7 @@
       <c r="AC407" s="24"/>
       <c r="AD407" s="24"/>
     </row>
-    <row r="408" spans="1:30">
+    <row r="408" spans="1:30" ht="14">
       <c r="A408" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22447,7 +22457,7 @@
       <c r="AC408" s="24"/>
       <c r="AD408" s="24"/>
     </row>
-    <row r="409" spans="1:30">
+    <row r="409" spans="1:30" ht="14">
       <c r="A409" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22481,7 +22491,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="410" spans="1:30">
+    <row r="410" spans="1:30" ht="14">
       <c r="A410" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22515,7 +22525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="411" spans="1:30">
+    <row r="411" spans="1:30" ht="14">
       <c r="A411" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22573,7 +22583,7 @@
       <c r="AC411" s="24"/>
       <c r="AD411" s="24"/>
     </row>
-    <row r="412" spans="1:30">
+    <row r="412" spans="1:30" ht="14">
       <c r="A412" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22607,7 +22617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="413" spans="1:30">
+    <row r="413" spans="1:30" ht="14">
       <c r="A413" s="6" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22641,7 +22651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="414" spans="1:30">
+    <row r="414" spans="1:30" ht="14">
       <c r="A414" s="53" t="e">
         <f t="shared" ca="1" si="4"/>
         <v>#NAME?</v>
@@ -22699,7 +22709,7 @@
       <c r="AC414" s="21"/>
       <c r="AD414" s="21"/>
     </row>
-    <row r="415" spans="1:30">
+    <row r="415" spans="1:30" ht="14">
       <c r="A415" s="6" t="e">
         <f t="shared" ref="A415:A503" ca="1" si="6">_xludf.CONCAT(C415," (RS)")</f>
         <v>#NAME?</v>
@@ -22733,7 +22743,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="416" spans="1:30">
+    <row r="416" spans="1:30" ht="14">
       <c r="A416" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -22767,7 +22777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="417" spans="1:30">
+    <row r="417" spans="1:30" ht="14">
       <c r="A417" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -22807,7 +22817,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="418" spans="1:30">
+    <row r="418" spans="1:30" ht="14">
       <c r="A418" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -22847,7 +22857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="419" spans="1:30">
+    <row r="419" spans="1:30" ht="14">
       <c r="A419" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -22881,7 +22891,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="420" spans="1:30">
+    <row r="420" spans="1:30" ht="14">
       <c r="A420" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -22921,7 +22931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="421" spans="1:30">
+    <row r="421" spans="1:30" ht="14">
       <c r="A421" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -22979,7 +22989,7 @@
       <c r="AC421" s="24"/>
       <c r="AD421" s="24"/>
     </row>
-    <row r="422" spans="1:30">
+    <row r="422" spans="1:30" ht="14">
       <c r="A422" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23013,7 +23023,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="423" spans="1:30">
+    <row r="423" spans="1:30" ht="14">
       <c r="A423" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23071,7 +23081,7 @@
       <c r="AC423" s="24"/>
       <c r="AD423" s="24"/>
     </row>
-    <row r="424" spans="1:30">
+    <row r="424" spans="1:30" ht="14">
       <c r="A424" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23111,7 +23121,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="425" spans="1:30">
+    <row r="425" spans="1:30" ht="14">
       <c r="A425" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23169,7 +23179,7 @@
       <c r="AC425" s="24"/>
       <c r="AD425" s="24"/>
     </row>
-    <row r="426" spans="1:30">
+    <row r="426" spans="1:30" ht="14">
       <c r="A426" s="53" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23227,7 +23237,7 @@
       <c r="AC426" s="21"/>
       <c r="AD426" s="21"/>
     </row>
-    <row r="427" spans="1:30">
+    <row r="427" spans="1:30" ht="14">
       <c r="A427" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23267,7 +23277,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="428" spans="1:30">
+    <row r="428" spans="1:30" ht="14">
       <c r="A428" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23307,7 +23317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="429" spans="1:30">
+    <row r="429" spans="1:30" ht="14">
       <c r="A429" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23341,7 +23351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="430" spans="1:30">
+    <row r="430" spans="1:30" ht="14">
       <c r="A430" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23375,7 +23385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="431" spans="1:30">
+    <row r="431" spans="1:30" ht="14">
       <c r="A431" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23433,7 +23443,7 @@
       <c r="AC431" s="24"/>
       <c r="AD431" s="24"/>
     </row>
-    <row r="432" spans="1:30">
+    <row r="432" spans="1:30" ht="14">
       <c r="A432" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23467,7 +23477,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="433" spans="1:30">
+    <row r="433" spans="1:30" ht="14">
       <c r="A433" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23525,7 +23535,7 @@
       <c r="AC433" s="24"/>
       <c r="AD433" s="24"/>
     </row>
-    <row r="434" spans="1:30">
+    <row r="434" spans="1:30" ht="14">
       <c r="A434" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23583,7 +23593,7 @@
       <c r="AC434" s="24"/>
       <c r="AD434" s="24"/>
     </row>
-    <row r="435" spans="1:30">
+    <row r="435" spans="1:30" ht="14">
       <c r="A435" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23641,7 +23651,7 @@
       <c r="AC435" s="32"/>
       <c r="AD435" s="32"/>
     </row>
-    <row r="436" spans="1:30">
+    <row r="436" spans="1:30" ht="14">
       <c r="A436" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23699,7 +23709,7 @@
       <c r="AC436" s="32"/>
       <c r="AD436" s="32"/>
     </row>
-    <row r="437" spans="1:30">
+    <row r="437" spans="1:30" ht="14">
       <c r="A437" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23757,7 +23767,7 @@
       <c r="AC437" s="24"/>
       <c r="AD437" s="24"/>
     </row>
-    <row r="438" spans="1:30">
+    <row r="438" spans="1:30" ht="14">
       <c r="A438" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23791,7 +23801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="439" spans="1:30">
+    <row r="439" spans="1:30" ht="14">
       <c r="A439" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23849,7 +23859,7 @@
       <c r="AC439" s="32"/>
       <c r="AD439" s="32"/>
     </row>
-    <row r="440" spans="1:30">
+    <row r="440" spans="1:30" ht="14">
       <c r="A440" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23887,7 +23897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="441" spans="1:30">
+    <row r="441" spans="1:30" ht="14">
       <c r="A441" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23921,7 +23931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="442" spans="1:30">
+    <row r="442" spans="1:30" ht="14">
       <c r="A442" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -23955,7 +23965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="443" spans="1:30">
+    <row r="443" spans="1:30" ht="14">
       <c r="A443" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24013,7 +24023,7 @@
       <c r="AC443" s="24"/>
       <c r="AD443" s="24"/>
     </row>
-    <row r="444" spans="1:30">
+    <row r="444" spans="1:30" ht="14">
       <c r="A444" s="53" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24071,7 +24081,7 @@
       <c r="AC444" s="21"/>
       <c r="AD444" s="21"/>
     </row>
-    <row r="445" spans="1:30">
+    <row r="445" spans="1:30" ht="14">
       <c r="A445" s="53" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24129,7 +24139,7 @@
       <c r="AC445" s="21"/>
       <c r="AD445" s="21"/>
     </row>
-    <row r="446" spans="1:30">
+    <row r="446" spans="1:30" ht="14">
       <c r="A446" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24187,7 +24197,7 @@
       <c r="AC446" s="32"/>
       <c r="AD446" s="32"/>
     </row>
-    <row r="447" spans="1:30">
+    <row r="447" spans="1:30" ht="14">
       <c r="A447" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24245,7 +24255,7 @@
       <c r="AC447" s="24"/>
       <c r="AD447" s="24"/>
     </row>
-    <row r="448" spans="1:30">
+    <row r="448" spans="1:30" ht="14">
       <c r="A448" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24303,7 +24313,7 @@
       <c r="AC448" s="24"/>
       <c r="AD448" s="24"/>
     </row>
-    <row r="449" spans="1:30">
+    <row r="449" spans="1:30" ht="14">
       <c r="A449" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24359,7 +24369,7 @@
       <c r="AC449" s="99"/>
       <c r="AD449" s="99"/>
     </row>
-    <row r="450" spans="1:30">
+    <row r="450" spans="1:30" ht="14">
       <c r="A450" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24393,7 +24403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="451" spans="1:30">
+    <row r="451" spans="1:30" ht="14">
       <c r="A451" s="53" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24451,7 +24461,7 @@
       <c r="AC451" s="21"/>
       <c r="AD451" s="21"/>
     </row>
-    <row r="452" spans="1:30">
+    <row r="452" spans="1:30" ht="14">
       <c r="A452" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24485,7 +24495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="453" spans="1:30">
+    <row r="453" spans="1:30" ht="14">
       <c r="A453" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24543,7 +24553,7 @@
       <c r="AC453" s="24"/>
       <c r="AD453" s="24"/>
     </row>
-    <row r="454" spans="1:30">
+    <row r="454" spans="1:30" ht="14">
       <c r="A454" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24601,7 +24611,7 @@
       <c r="AC454" s="24"/>
       <c r="AD454" s="24"/>
     </row>
-    <row r="455" spans="1:30">
+    <row r="455" spans="1:30" ht="14">
       <c r="A455" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24659,7 +24669,7 @@
       <c r="AC455" s="24"/>
       <c r="AD455" s="24"/>
     </row>
-    <row r="456" spans="1:30">
+    <row r="456" spans="1:30" ht="14">
       <c r="A456" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24693,7 +24703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="457" spans="1:30">
+    <row r="457" spans="1:30" ht="14">
       <c r="A457" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24727,7 +24737,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="458" spans="1:30">
+    <row r="458" spans="1:30" ht="14">
       <c r="A458" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24785,7 +24795,7 @@
       <c r="AC458" s="24"/>
       <c r="AD458" s="24"/>
     </row>
-    <row r="459" spans="1:30">
+    <row r="459" spans="1:30" ht="14">
       <c r="A459" s="53" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24843,7 +24853,7 @@
       <c r="AC459" s="21"/>
       <c r="AD459" s="21"/>
     </row>
-    <row r="460" spans="1:30">
+    <row r="460" spans="1:30" ht="14">
       <c r="A460" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24901,7 +24911,7 @@
       <c r="AC460" s="24"/>
       <c r="AD460" s="24"/>
     </row>
-    <row r="461" spans="1:30">
+    <row r="461" spans="1:30" ht="14">
       <c r="A461" s="53" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -24959,7 +24969,7 @@
       <c r="AC461" s="78"/>
       <c r="AD461" s="78"/>
     </row>
-    <row r="462" spans="1:30">
+    <row r="462" spans="1:30" ht="14">
       <c r="A462" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25017,7 +25027,7 @@
       <c r="AC462" s="24"/>
       <c r="AD462" s="24"/>
     </row>
-    <row r="463" spans="1:30">
+    <row r="463" spans="1:30" ht="14">
       <c r="A463" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25075,7 +25085,7 @@
       <c r="AC463" s="24"/>
       <c r="AD463" s="24"/>
     </row>
-    <row r="464" spans="1:30">
+    <row r="464" spans="1:30" ht="14">
       <c r="A464" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25109,7 +25119,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="465" spans="1:30">
+    <row r="465" spans="1:30" ht="14">
       <c r="A465" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25167,7 +25177,7 @@
       <c r="AC465" s="24"/>
       <c r="AD465" s="24"/>
     </row>
-    <row r="466" spans="1:30">
+    <row r="466" spans="1:30" ht="14">
       <c r="A466" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25207,7 +25217,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="467" spans="1:30">
+    <row r="467" spans="1:30" ht="14">
       <c r="A467" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25241,7 +25251,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="468" spans="1:30">
+    <row r="468" spans="1:30" ht="14">
       <c r="A468" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25281,7 +25291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="469" spans="1:30">
+    <row r="469" spans="1:30" ht="14">
       <c r="A469" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25339,7 +25349,7 @@
       <c r="AC469" s="32"/>
       <c r="AD469" s="32"/>
     </row>
-    <row r="470" spans="1:30">
+    <row r="470" spans="1:30" ht="14">
       <c r="A470" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25373,7 +25383,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="471" spans="1:30">
+    <row r="471" spans="1:30" ht="14">
       <c r="A471" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25407,7 +25417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="472" spans="1:30">
+    <row r="472" spans="1:30" ht="14">
       <c r="A472" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25465,7 +25475,7 @@
       <c r="AC472" s="24"/>
       <c r="AD472" s="24"/>
     </row>
-    <row r="473" spans="1:30">
+    <row r="473" spans="1:30" ht="14">
       <c r="A473" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25499,7 +25509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="474" spans="1:30">
+    <row r="474" spans="1:30" ht="14">
       <c r="A474" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25557,7 +25567,7 @@
       <c r="AC474" s="24"/>
       <c r="AD474" s="24"/>
     </row>
-    <row r="475" spans="1:30">
+    <row r="475" spans="1:30" ht="14">
       <c r="A475" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25591,7 +25601,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="476" spans="1:30">
+    <row r="476" spans="1:30" ht="14">
       <c r="A476" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25649,7 +25659,7 @@
       <c r="AC476" s="24"/>
       <c r="AD476" s="24"/>
     </row>
-    <row r="477" spans="1:30">
+    <row r="477" spans="1:30" ht="14">
       <c r="A477" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25683,7 +25693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="478" spans="1:30">
+    <row r="478" spans="1:30" ht="14">
       <c r="A478" s="53" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25741,7 +25751,7 @@
       <c r="AC478" s="21"/>
       <c r="AD478" s="21"/>
     </row>
-    <row r="479" spans="1:30">
+    <row r="479" spans="1:30" ht="14">
       <c r="A479" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25775,7 +25785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="480" spans="1:30">
+    <row r="480" spans="1:30" ht="14">
       <c r="A480" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25809,7 +25819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="481" spans="1:30">
+    <row r="481" spans="1:30" ht="14">
       <c r="A481" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25867,7 +25877,7 @@
       <c r="AC481" s="24"/>
       <c r="AD481" s="24"/>
     </row>
-    <row r="482" spans="1:30">
+    <row r="482" spans="1:30" ht="14">
       <c r="A482" s="79" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25925,7 +25935,7 @@
       <c r="AC482" s="32"/>
       <c r="AD482" s="32"/>
     </row>
-    <row r="483" spans="1:30">
+    <row r="483" spans="1:30" ht="14">
       <c r="A483" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -25983,7 +25993,7 @@
       <c r="AC483" s="24"/>
       <c r="AD483" s="24"/>
     </row>
-    <row r="484" spans="1:30">
+    <row r="484" spans="1:30" ht="14">
       <c r="A484" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26017,7 +26027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="485" spans="1:30">
+    <row r="485" spans="1:30" ht="14">
       <c r="A485" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26075,7 +26085,7 @@
       <c r="AC485" s="24"/>
       <c r="AD485" s="24"/>
     </row>
-    <row r="486" spans="1:30">
+    <row r="486" spans="1:30" ht="14">
       <c r="A486" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26133,7 +26143,7 @@
       <c r="AC486" s="32"/>
       <c r="AD486" s="32"/>
     </row>
-    <row r="487" spans="1:30">
+    <row r="487" spans="1:30" ht="14">
       <c r="A487" s="79" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26191,7 +26201,7 @@
       <c r="AC487" s="32"/>
       <c r="AD487" s="32"/>
     </row>
-    <row r="488" spans="1:30">
+    <row r="488" spans="1:30" ht="14">
       <c r="A488" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26249,7 +26259,7 @@
       <c r="AC488" s="24"/>
       <c r="AD488" s="24"/>
     </row>
-    <row r="489" spans="1:30">
+    <row r="489" spans="1:30" ht="14">
       <c r="A489" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26307,7 +26317,7 @@
       <c r="AC489" s="32"/>
       <c r="AD489" s="32"/>
     </row>
-    <row r="490" spans="1:30">
+    <row r="490" spans="1:30" ht="14">
       <c r="A490" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26365,7 +26375,7 @@
       <c r="AC490" s="32"/>
       <c r="AD490" s="32"/>
     </row>
-    <row r="491" spans="1:30">
+    <row r="491" spans="1:30" ht="14">
       <c r="A491" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26423,7 +26433,7 @@
       <c r="AC491" s="24"/>
       <c r="AD491" s="24"/>
     </row>
-    <row r="492" spans="1:30">
+    <row r="492" spans="1:30" ht="14">
       <c r="A492" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26457,7 +26467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="493" spans="1:30">
+    <row r="493" spans="1:30" ht="14">
       <c r="A493" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26515,7 +26525,7 @@
       <c r="AC493" s="24"/>
       <c r="AD493" s="24"/>
     </row>
-    <row r="494" spans="1:30">
+    <row r="494" spans="1:30" ht="14">
       <c r="A494" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26573,7 +26583,7 @@
       <c r="AC494" s="24"/>
       <c r="AD494" s="24"/>
     </row>
-    <row r="495" spans="1:30">
+    <row r="495" spans="1:30" ht="14">
       <c r="A495" s="53" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26631,7 +26641,7 @@
       <c r="AC495" s="78"/>
       <c r="AD495" s="78"/>
     </row>
-    <row r="496" spans="1:30">
+    <row r="496" spans="1:30" ht="14">
       <c r="A496" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26689,7 +26699,7 @@
       <c r="AC496" s="24"/>
       <c r="AD496" s="24"/>
     </row>
-    <row r="497" spans="1:30">
+    <row r="497" spans="1:30" ht="14">
       <c r="A497" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26724,7 +26734,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="498" spans="1:30">
+    <row r="498" spans="1:30" ht="14">
       <c r="A498" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26758,7 +26768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="499" spans="1:30">
+    <row r="499" spans="1:30" ht="14">
       <c r="A499" s="53" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26816,7 +26826,7 @@
       <c r="AC499" s="21"/>
       <c r="AD499" s="21"/>
     </row>
-    <row r="500" spans="1:30">
+    <row r="500" spans="1:30" ht="14">
       <c r="A500" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26850,7 +26860,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="501" spans="1:30">
+    <row r="501" spans="1:30" ht="14">
       <c r="A501" s="6" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26908,7 +26918,7 @@
       <c r="AC501" s="24"/>
       <c r="AD501" s="24"/>
     </row>
-    <row r="502" spans="1:30">
+    <row r="502" spans="1:30" ht="14">
       <c r="A502" s="53" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
@@ -26966,7 +26976,7 @@
       <c r="AC502" s="21"/>
       <c r="AD502" s="21"/>
     </row>
-    <row r="503" spans="1:30">
+    <row r="503" spans="1:30" ht="14">
       <c r="A503" s="53" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
